--- a/data/trans_camb/IP16B01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Edad-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,83; 100,0</t>
+          <t>85,83; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,04; 100,0</t>
+          <t>75,34; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,46; 100,0</t>
+          <t>79,98; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 100,0</t>
+          <t>92,94; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,68; 98,22</t>
+          <t>84,37; 98,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,19; 88,08</t>
+          <t>65,27; 87,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,99; 89,44</t>
+          <t>66,59; 89,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,6; 95,81</t>
+          <t>81,09; 96,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 97,46</t>
+          <t>74,85; 97,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,87; 91,18</t>
+          <t>78,14; 90,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,69; 91,3</t>
+          <t>75,51; 91,39</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>693,96; —</t>
+          <t>732,11; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645,16; —</t>
+          <t>750,73; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1637,37; —</t>
+          <t>1757,71; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1713,1; —</t>
+          <t>1775,54; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,76; 87,95</t>
+          <t>44,5; 87,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,01; 93,82</t>
+          <t>66,42; 94,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,2; 100,0</t>
+          <t>80,05; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,23; 84,65</t>
+          <t>40,34; 87,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,25; 91,36</t>
+          <t>64,56; 91,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,45; 88,39</t>
+          <t>63,89; 87,7</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,23; 88,9</t>
+          <t>55,81; 89,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,3; 80,29</t>
+          <t>30,17; 82,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,57; 100,0</t>
+          <t>56,3; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,68; 88,42</t>
+          <t>65,0; 88,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,0; 92,67</t>
+          <t>63,55; 92,45</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,24; 86,95</t>
+          <t>74,06; 87,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,36; 87,82</t>
+          <t>72,17; 87,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,27; 90,84</t>
+          <t>83,07; 90,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79,33; 89,01</t>
+          <t>78,98; 88,59</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2147,22; —</t>
+          <t>2177,73; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2188,07; —</t>
+          <t>2006,35; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5034,97; —</t>
+          <t>5681,2; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4693,67; —</t>
+          <t>5285,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Edad-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,83; 100,0</t>
+          <t>83,56; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,34; 100,0</t>
+          <t>71,79; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,98; 100,0</t>
+          <t>76,62; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,94; 100,0</t>
+          <t>92,74; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,37; 98,23</t>
+          <t>83,36; 98,25</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,27; 87,66</t>
+          <t>67,76; 88,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,59; 89,95</t>
+          <t>63,5; 89,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,09; 96,19</t>
+          <t>81,55; 96,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,85; 97,49</t>
+          <t>76,51; 97,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,14; 90,75</t>
+          <t>78,51; 91,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,51; 91,39</t>
+          <t>75,61; 91,31</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>732,11; —</t>
+          <t>671,17; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>750,73; —</t>
+          <t>599,56; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1757,71; —</t>
+          <t>1566,42; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1775,54; —</t>
+          <t>1569,62; —</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,5; 87,48</t>
+          <t>45,26; 86,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,42; 94,18</t>
+          <t>66,67; 93,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,05; 100,0</t>
+          <t>77,76; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,34; 87,02</t>
+          <t>42,23; 85,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,56; 91,85</t>
+          <t>67,91; 93,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,89; 87,7</t>
+          <t>63,04; 87,62</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,81; 89,05</t>
+          <t>55,73; 89,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,17; 82,01</t>
+          <t>26,86; 79,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,3; 100,0</t>
+          <t>58,73; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,0; 88,35</t>
+          <t>61,92; 88,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,55; 92,45</t>
+          <t>61,54; 91,36</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,06; 87,17</t>
+          <t>73,61; 87,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,17; 87,06</t>
+          <t>72,02; 86,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,07; 90,83</t>
+          <t>83,1; 90,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78,98; 88,59</t>
+          <t>78,97; 88,82</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2177,73; —</t>
+          <t>2357,06; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2006,35; —</t>
+          <t>2324,28; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5681,2; —</t>
+          <t>4396,5; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5285,63; —</t>
+          <t>4694,45; —</t>
         </is>
       </c>
     </row>
